--- a/src/main/resources/Export/TournamentInfo_2.xlsx
+++ b/src/main/resources/Export/TournamentInfo_2.xlsx
@@ -20,7 +20,7 @@
     <t>Tên giải đấu: V-League 2026</t>
   </si>
   <si>
-    <t>Ngày bắt đầu: 2025-06-21</t>
+    <t>Ngày bắt đầu: 2025-08-13</t>
   </si>
   <si>
     <t>Ngày kết thúc: 2026-06-15</t>
